--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260820.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260820.xlsx
@@ -733,17 +733,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>438,250,032</t>
+          <t>84,896,365</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -755,17 +755,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>84,896,365</t>
+          <t>438,250,032</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>148,023,589</t>
+          <t>25,492,416</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>25,492,416</t>
+          <t>148,023,589</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>信邦</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>32,664,980</t>
+          <t>10,993,950</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>信邦</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>10,993,950</t>
+          <t>32,664,980</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
